--- a/Result/profitability/2062.xlsx
+++ b/Result/profitability/2062.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.16375</v>
+        <v>0.14</v>
       </c>
       <c r="N2" t="n">
-        <v>11.36875</v>
+        <v>11.06375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2025</v>
+        <v>0.1575</v>
       </c>
       <c r="N3" t="n">
-        <v>11.79625</v>
+        <v>11.74375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2725000000000001</v>
+        <v>0.2725</v>
       </c>
       <c r="N4" t="n">
-        <v>12.995</v>
+        <v>12.9375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25375</v>
+        <v>0.2625</v>
       </c>
       <c r="N5" t="n">
-        <v>12.8325</v>
+        <v>13.2425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.275</v>
+        <v>0.315</v>
       </c>
       <c r="N6" t="n">
-        <v>13.51625</v>
+        <v>14.06875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.385</v>
+        <v>0.3825</v>
       </c>
       <c r="N7" t="n">
-        <v>15.77625</v>
+        <v>15.8125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.88</v>
       </c>
       <c r="M8" t="n">
-        <v>0.46875</v>
+        <v>0.4925</v>
       </c>
       <c r="N8" t="n">
-        <v>17.1575</v>
+        <v>17.2825</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.68</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5537500000000001</v>
+        <v>0.55375</v>
       </c>
       <c r="N9" t="n">
         <v>18.8725</v>
@@ -1772,7 +1772,7 @@
         <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7550000000000001</v>
+        <v>0.755</v>
       </c>
       <c r="N11" t="n">
         <v>21.35125</v>
@@ -9826,6 +9826,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1857</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1642</v>
+      </c>
+      <c r="E75" t="n">
+        <v>215</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>72</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>39</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.89125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09433962264150941</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.279999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3942307692307692</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
